--- a/shops.xlsx
+++ b/shops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512a546b848d6679/سطح المكتب/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="426" documentId="11_9888CF1E5976440F62355476585DCE3A474BFA2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC358B25-B801-4563-BD93-FB72D7A848FF}"/>
+  <xr:revisionPtr revIDLastSave="431" documentId="11_9888CF1E5976440F62355476585DCE3A474BFA2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{012873F6-791F-446A-AED9-2F3C028F514F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="272">
   <si>
     <t>اسم المحل</t>
   </si>
@@ -164,9 +164,6 @@
   </si>
   <si>
     <t>Damas</t>
-  </si>
-  <si>
-    <t>إكسسوارات ومجوهرات</t>
   </si>
   <si>
     <t>Accessories &amp; Jewelry</t>
@@ -1205,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -1240,30 +1237,30 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
         <v>93</v>
       </c>
-      <c r="B2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>94</v>
-      </c>
-      <c r="F2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
@@ -1272,10 +1269,10 @@
         <v>24</v>
       </c>
       <c r="E3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" t="s">
         <v>94</v>
-      </c>
-      <c r="F3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1283,7 +1280,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -1295,7 +1292,7 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1303,7 +1300,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -1315,7 +1312,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1323,7 +1320,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -1335,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1355,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1375,7 +1372,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1395,15 +1392,15 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
@@ -1415,15 +1412,15 @@
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" t="s">
         <v>110</v>
-      </c>
-      <c r="B11" t="s">
-        <v>111</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
@@ -1435,15 +1432,15 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" t="s">
         <v>110</v>
-      </c>
-      <c r="B12" t="s">
-        <v>111</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -1455,15 +1452,15 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" t="s">
         <v>110</v>
-      </c>
-      <c r="B13" t="s">
-        <v>111</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
@@ -1475,15 +1472,15 @@
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" t="s">
         <v>112</v>
-      </c>
-      <c r="B14" t="s">
-        <v>113</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
@@ -1495,15 +1492,15 @@
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" t="s">
         <v>112</v>
-      </c>
-      <c r="B15" t="s">
-        <v>113</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -1515,15 +1512,15 @@
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" t="s">
         <v>112</v>
-      </c>
-      <c r="B16" t="s">
-        <v>113</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -1535,15 +1532,15 @@
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" t="s">
         <v>114</v>
-      </c>
-      <c r="B17" t="s">
-        <v>115</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
@@ -1555,15 +1552,15 @@
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" t="s">
         <v>114</v>
-      </c>
-      <c r="B18" t="s">
-        <v>115</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
@@ -1575,15 +1572,15 @@
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" t="s">
         <v>114</v>
-      </c>
-      <c r="B19" t="s">
-        <v>115</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
@@ -1595,16 +1592,16 @@
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" t="s">
         <v>89</v>
       </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
       <c r="C20" t="s">
         <v>23</v>
       </c>
@@ -1612,18 +1609,18 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" t="s">
         <v>116</v>
-      </c>
-      <c r="F20" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" t="s">
         <v>118</v>
-      </c>
-      <c r="B21" t="s">
-        <v>119</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
@@ -1632,38 +1629,38 @@
         <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" t="s">
         <v>122</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" t="s">
         <v>123</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" t="s">
-        <v>125</v>
-      </c>
-      <c r="F22" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C23" t="s">
         <v>21</v>
@@ -1672,18 +1669,18 @@
         <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
@@ -1692,35 +1689,35 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" t="s">
         <v>57</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" t="s">
         <v>129</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" t="s">
         <v>130</v>
-      </c>
-      <c r="C25" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
         <v>39</v>
@@ -1735,15 +1732,15 @@
         <v>31</v>
       </c>
       <c r="F26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" t="s">
         <v>134</v>
-      </c>
-      <c r="B27" t="s">
-        <v>135</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
@@ -1760,11 +1757,11 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
         <v>99</v>
       </c>
-      <c r="B28" t="s">
-        <v>100</v>
-      </c>
       <c r="C28" t="s">
         <v>23</v>
       </c>
@@ -1772,18 +1769,18 @@
         <v>24</v>
       </c>
       <c r="E28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" t="s">
         <v>94</v>
-      </c>
-      <c r="F28" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
@@ -1795,35 +1792,35 @@
         <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" t="s">
         <v>139</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" t="s">
         <v>140</v>
       </c>
-      <c r="C30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>141</v>
-      </c>
-      <c r="F30" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
@@ -1835,15 +1832,15 @@
         <v>29</v>
       </c>
       <c r="F31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" t="s">
         <v>145</v>
-      </c>
-      <c r="B32" t="s">
-        <v>146</v>
       </c>
       <c r="C32" t="s">
         <v>23</v>
@@ -1855,15 +1852,15 @@
         <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C33" t="s">
         <v>23</v>
@@ -1872,18 +1869,18 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F33" t="s">
         <v>48</v>
-      </c>
-      <c r="F33" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
@@ -1900,10 +1897,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
@@ -1912,19 +1909,19 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" t="s">
         <v>48</v>
-      </c>
-      <c r="F35" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" t="s">
         <v>97</v>
       </c>
-      <c r="B36" t="s">
-        <v>98</v>
-      </c>
       <c r="C36" t="s">
         <v>23</v>
       </c>
@@ -1932,18 +1929,18 @@
         <v>24</v>
       </c>
       <c r="E36" t="s">
+        <v>93</v>
+      </c>
+      <c r="F36" t="s">
         <v>94</v>
-      </c>
-      <c r="F36" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
@@ -1960,10 +1957,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -1975,12 +1972,12 @@
         <v>31</v>
       </c>
       <c r="F38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
@@ -1992,19 +1989,19 @@
         <v>24</v>
       </c>
       <c r="E39" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" t="s">
         <v>94</v>
-      </c>
-      <c r="F39" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>179</v>
+      </c>
+      <c r="B40" t="s">
         <v>180</v>
       </c>
-      <c r="B40" t="s">
-        <v>181</v>
-      </c>
       <c r="C40" t="s">
         <v>23</v>
       </c>
@@ -2012,19 +2009,19 @@
         <v>24</v>
       </c>
       <c r="E40" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" t="s">
         <v>94</v>
-      </c>
-      <c r="F40" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>181</v>
+      </c>
+      <c r="B41" t="s">
         <v>182</v>
       </c>
-      <c r="B41" t="s">
-        <v>183</v>
-      </c>
       <c r="C41" t="s">
         <v>23</v>
       </c>
@@ -2032,19 +2029,19 @@
         <v>24</v>
       </c>
       <c r="E41" t="s">
+        <v>163</v>
+      </c>
+      <c r="F41" t="s">
         <v>48</v>
-      </c>
-      <c r="F41" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" t="s">
         <v>84</v>
       </c>
-      <c r="B42" t="s">
-        <v>85</v>
-      </c>
       <c r="C42" t="s">
         <v>23</v>
       </c>
@@ -2052,10 +2049,10 @@
         <v>24</v>
       </c>
       <c r="E42" t="s">
+        <v>79</v>
+      </c>
+      <c r="F42" t="s">
         <v>80</v>
-      </c>
-      <c r="F42" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2063,7 +2060,7 @@
         <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
@@ -2075,7 +2072,7 @@
         <v>9</v>
       </c>
       <c r="F43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2092,18 +2089,18 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C45" t="s">
         <v>23</v>
@@ -2112,10 +2109,10 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2135,15 +2132,15 @@
         <v>31</v>
       </c>
       <c r="F46" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B47" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -2152,15 +2149,15 @@
         <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
@@ -2175,12 +2172,12 @@
         <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
@@ -2195,7 +2192,7 @@
         <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2215,15 +2212,15 @@
         <v>29</v>
       </c>
       <c r="F50" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B51" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C51" t="s">
         <v>23</v>
@@ -2235,12 +2232,12 @@
         <v>31</v>
       </c>
       <c r="F51" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B52" t="s">
         <v>40</v>
@@ -2255,15 +2252,15 @@
         <v>31</v>
       </c>
       <c r="F52" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
@@ -2272,18 +2269,18 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" t="s">
         <v>94</v>
-      </c>
-      <c r="F53" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B54" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
@@ -2292,10 +2289,10 @@
         <v>24</v>
       </c>
       <c r="E54" t="s">
+        <v>140</v>
+      </c>
+      <c r="F54" t="s">
         <v>141</v>
-      </c>
-      <c r="F54" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2303,7 +2300,7 @@
         <v>41</v>
       </c>
       <c r="B55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
@@ -2315,12 +2312,12 @@
         <v>31</v>
       </c>
       <c r="F55" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B56" t="s">
         <v>20</v>
@@ -2335,15 +2332,15 @@
         <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B57" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C57" t="s">
         <v>23</v>
@@ -2355,16 +2352,16 @@
         <v>31</v>
       </c>
       <c r="F57" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" t="s">
         <v>186</v>
       </c>
-      <c r="B58" t="s">
-        <v>187</v>
-      </c>
       <c r="C58" t="s">
         <v>23</v>
       </c>
@@ -2372,18 +2369,18 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
+        <v>79</v>
+      </c>
+      <c r="F58" t="s">
         <v>80</v>
-      </c>
-      <c r="F58" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B59" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C59" t="s">
         <v>7</v>
@@ -2395,7 +2392,7 @@
         <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2415,15 +2412,15 @@
         <v>31</v>
       </c>
       <c r="F60" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -2432,18 +2429,18 @@
         <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B62" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C62" t="s">
         <v>23</v>
@@ -2452,18 +2449,18 @@
         <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F62" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B63" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C63" t="s">
         <v>23</v>
@@ -2472,19 +2469,19 @@
         <v>24</v>
       </c>
       <c r="E63" t="s">
+        <v>100</v>
+      </c>
+      <c r="F63" t="s">
         <v>101</v>
-      </c>
-      <c r="F63" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>51</v>
+      </c>
+      <c r="B64" t="s">
         <v>52</v>
       </c>
-      <c r="B64" t="s">
-        <v>53</v>
-      </c>
       <c r="C64" t="s">
         <v>23</v>
       </c>
@@ -2492,18 +2489,18 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F64" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B65" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
@@ -2515,15 +2512,15 @@
         <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B66" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C66" t="s">
         <v>23</v>
@@ -2532,18 +2529,18 @@
         <v>24</v>
       </c>
       <c r="E66" t="s">
+        <v>56</v>
+      </c>
+      <c r="F66" t="s">
         <v>57</v>
-      </c>
-      <c r="F66" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B67" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C67" t="s">
         <v>7</v>
@@ -2555,12 +2552,12 @@
         <v>9</v>
       </c>
       <c r="F67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
@@ -2575,12 +2572,12 @@
         <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
@@ -2592,15 +2589,15 @@
         <v>24</v>
       </c>
       <c r="E69" t="s">
+        <v>56</v>
+      </c>
+      <c r="F69" t="s">
         <v>57</v>
-      </c>
-      <c r="F69" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
@@ -2615,12 +2612,12 @@
         <v>9</v>
       </c>
       <c r="F70" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
@@ -2635,12 +2632,12 @@
         <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
@@ -2652,15 +2649,15 @@
         <v>24</v>
       </c>
       <c r="E72" t="s">
+        <v>56</v>
+      </c>
+      <c r="F72" t="s">
         <v>57</v>
-      </c>
-      <c r="F72" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
@@ -2675,15 +2672,15 @@
         <v>9</v>
       </c>
       <c r="F73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B74" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C74" t="s">
         <v>23</v>
@@ -2695,15 +2692,15 @@
         <v>31</v>
       </c>
       <c r="F74" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>191</v>
+      </c>
+      <c r="B75" t="s">
         <v>192</v>
-      </c>
-      <c r="B75" t="s">
-        <v>193</v>
       </c>
       <c r="C75" t="s">
         <v>23</v>
@@ -2715,12 +2712,12 @@
         <v>31</v>
       </c>
       <c r="F75" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>
@@ -2735,12 +2732,12 @@
         <v>9</v>
       </c>
       <c r="F76" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B77" t="s">
         <v>6</v>
@@ -2755,12 +2752,12 @@
         <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B78" t="s">
         <v>6</v>
@@ -2775,7 +2772,7 @@
         <v>9</v>
       </c>
       <c r="F78" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2783,7 +2780,7 @@
         <v>35</v>
       </c>
       <c r="B79" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C79" t="s">
         <v>23</v>
@@ -2795,16 +2792,16 @@
         <v>31</v>
       </c>
       <c r="F79" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" t="s">
         <v>82</v>
       </c>
-      <c r="B80" t="s">
-        <v>83</v>
-      </c>
       <c r="C80" t="s">
         <v>23</v>
       </c>
@@ -2812,18 +2809,18 @@
         <v>24</v>
       </c>
       <c r="E80" t="s">
+        <v>79</v>
+      </c>
+      <c r="F80" t="s">
         <v>80</v>
-      </c>
-      <c r="F80" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C81" t="s">
         <v>23</v>
@@ -2832,10 +2829,10 @@
         <v>24</v>
       </c>
       <c r="E81" t="s">
+        <v>237</v>
+      </c>
+      <c r="F81" t="s">
         <v>238</v>
-      </c>
-      <c r="F81" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2843,7 +2840,7 @@
         <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
@@ -2855,7 +2852,7 @@
         <v>31</v>
       </c>
       <c r="F82" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2863,7 +2860,7 @@
         <v>30</v>
       </c>
       <c r="B83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
@@ -2875,15 +2872,15 @@
         <v>31</v>
       </c>
       <c r="F83" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B84" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C84" t="s">
         <v>23</v>
@@ -2895,15 +2892,15 @@
         <v>31</v>
       </c>
       <c r="F84" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>200</v>
+      </c>
+      <c r="B85" t="s">
         <v>201</v>
-      </c>
-      <c r="B85" t="s">
-        <v>202</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
@@ -2915,7 +2912,7 @@
         <v>31</v>
       </c>
       <c r="F85" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2935,12 +2932,12 @@
         <v>31</v>
       </c>
       <c r="F86" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B87" t="s">
         <v>10</v>
@@ -2955,12 +2952,12 @@
         <v>9</v>
       </c>
       <c r="F87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B88" t="s">
         <v>10</v>
@@ -2975,35 +2972,35 @@
         <v>9</v>
       </c>
       <c r="F88" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>54</v>
+      </c>
+      <c r="B89" t="s">
         <v>55</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" t="s">
         <v>56</v>
       </c>
-      <c r="C89" t="s">
-        <v>23</v>
-      </c>
-      <c r="D89" t="s">
-        <v>24</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>57</v>
-      </c>
-      <c r="F89" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>203</v>
+      </c>
+      <c r="B90" t="s">
         <v>204</v>
-      </c>
-      <c r="B90" t="s">
-        <v>205</v>
       </c>
       <c r="C90" t="s">
         <v>17</v>
@@ -3015,16 +3012,16 @@
         <v>9</v>
       </c>
       <c r="F90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>205</v>
+      </c>
+      <c r="B91" t="s">
         <v>206</v>
       </c>
-      <c r="B91" t="s">
-        <v>207</v>
-      </c>
       <c r="C91" t="s">
         <v>23</v>
       </c>
@@ -3032,19 +3029,19 @@
         <v>24</v>
       </c>
       <c r="E91" t="s">
+        <v>79</v>
+      </c>
+      <c r="F91" t="s">
         <v>80</v>
-      </c>
-      <c r="F91" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>68</v>
+      </c>
+      <c r="B92" t="s">
         <v>69</v>
       </c>
-      <c r="B92" t="s">
-        <v>70</v>
-      </c>
       <c r="C92" t="s">
         <v>23</v>
       </c>
@@ -3052,19 +3049,19 @@
         <v>24</v>
       </c>
       <c r="E92" t="s">
+        <v>61</v>
+      </c>
+      <c r="F92" t="s">
         <v>62</v>
-      </c>
-      <c r="F92" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>207</v>
+      </c>
+      <c r="B93" t="s">
         <v>208</v>
       </c>
-      <c r="B93" t="s">
-        <v>209</v>
-      </c>
       <c r="C93" t="s">
         <v>23</v>
       </c>
@@ -3072,19 +3069,19 @@
         <v>24</v>
       </c>
       <c r="E93" t="s">
+        <v>61</v>
+      </c>
+      <c r="F93" t="s">
         <v>62</v>
-      </c>
-      <c r="F93" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>63</v>
+      </c>
+      <c r="B94" t="s">
         <v>64</v>
       </c>
-      <c r="B94" t="s">
-        <v>65</v>
-      </c>
       <c r="C94" t="s">
         <v>23</v>
       </c>
@@ -3092,19 +3089,19 @@
         <v>24</v>
       </c>
       <c r="E94" t="s">
+        <v>61</v>
+      </c>
+      <c r="F94" t="s">
         <v>62</v>
-      </c>
-      <c r="F94" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>209</v>
+      </c>
+      <c r="B95" t="s">
         <v>210</v>
       </c>
-      <c r="B95" t="s">
-        <v>211</v>
-      </c>
       <c r="C95" t="s">
         <v>23</v>
       </c>
@@ -3112,19 +3109,19 @@
         <v>24</v>
       </c>
       <c r="E95" t="s">
+        <v>61</v>
+      </c>
+      <c r="F95" t="s">
         <v>62</v>
-      </c>
-      <c r="F95" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>211</v>
+      </c>
+      <c r="B96" t="s">
         <v>212</v>
       </c>
-      <c r="B96" t="s">
-        <v>213</v>
-      </c>
       <c r="C96" t="s">
         <v>23</v>
       </c>
@@ -3132,19 +3129,19 @@
         <v>24</v>
       </c>
       <c r="E96" t="s">
+        <v>61</v>
+      </c>
+      <c r="F96" t="s">
         <v>62</v>
-      </c>
-      <c r="F96" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97" t="s">
         <v>71</v>
       </c>
-      <c r="B97" t="s">
-        <v>72</v>
-      </c>
       <c r="C97" t="s">
         <v>23</v>
       </c>
@@ -3152,18 +3149,18 @@
         <v>24</v>
       </c>
       <c r="E97" t="s">
+        <v>61</v>
+      </c>
+      <c r="F97" t="s">
         <v>62</v>
-      </c>
-      <c r="F97" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B98" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C98" t="s">
         <v>23</v>
@@ -3172,19 +3169,19 @@
         <v>24</v>
       </c>
       <c r="E98" t="s">
+        <v>61</v>
+      </c>
+      <c r="F98" t="s">
         <v>62</v>
-      </c>
-      <c r="F98" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>213</v>
+      </c>
+      <c r="B99" t="s">
         <v>214</v>
       </c>
-      <c r="B99" t="s">
-        <v>215</v>
-      </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
@@ -3192,18 +3189,18 @@
         <v>24</v>
       </c>
       <c r="E99" t="s">
+        <v>61</v>
+      </c>
+      <c r="F99" t="s">
         <v>62</v>
-      </c>
-      <c r="F99" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B100" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
@@ -3212,19 +3209,19 @@
         <v>24</v>
       </c>
       <c r="E100" t="s">
+        <v>61</v>
+      </c>
+      <c r="F100" t="s">
         <v>62</v>
-      </c>
-      <c r="F100" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>216</v>
+      </c>
+      <c r="B101" t="s">
         <v>217</v>
       </c>
-      <c r="B101" t="s">
-        <v>218</v>
-      </c>
       <c r="C101" t="s">
         <v>23</v>
       </c>
@@ -3232,19 +3229,19 @@
         <v>24</v>
       </c>
       <c r="E101" t="s">
+        <v>61</v>
+      </c>
+      <c r="F101" t="s">
         <v>62</v>
-      </c>
-      <c r="F101" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>218</v>
+      </c>
+      <c r="B102" t="s">
         <v>219</v>
       </c>
-      <c r="B102" t="s">
-        <v>220</v>
-      </c>
       <c r="C102" t="s">
         <v>23</v>
       </c>
@@ -3252,18 +3249,18 @@
         <v>24</v>
       </c>
       <c r="E102" t="s">
+        <v>79</v>
+      </c>
+      <c r="F102" t="s">
         <v>80</v>
-      </c>
-      <c r="F102" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>220</v>
+      </c>
+      <c r="B103" t="s">
         <v>221</v>
-      </c>
-      <c r="B103" t="s">
-        <v>222</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
@@ -3275,15 +3272,15 @@
         <v>31</v>
       </c>
       <c r="F103" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B104" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C104" t="s">
         <v>23</v>
@@ -3295,16 +3292,16 @@
         <v>31</v>
       </c>
       <c r="F104" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>58</v>
+      </c>
+      <c r="B105" t="s">
         <v>59</v>
       </c>
-      <c r="B105" t="s">
-        <v>60</v>
-      </c>
       <c r="C105" t="s">
         <v>23</v>
       </c>
@@ -3312,15 +3309,15 @@
         <v>24</v>
       </c>
       <c r="E105" t="s">
+        <v>56</v>
+      </c>
+      <c r="F105" t="s">
         <v>57</v>
-      </c>
-      <c r="F105" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B106" t="s">
         <v>38</v>
@@ -3335,15 +3332,15 @@
         <v>31</v>
       </c>
       <c r="F106" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>224</v>
+      </c>
+      <c r="B107" t="s">
         <v>225</v>
-      </c>
-      <c r="B107" t="s">
-        <v>226</v>
       </c>
       <c r="C107" t="s">
         <v>7</v>
@@ -3355,15 +3352,15 @@
         <v>9</v>
       </c>
       <c r="F107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>226</v>
+      </c>
+      <c r="B108" t="s">
         <v>227</v>
-      </c>
-      <c r="B108" t="s">
-        <v>228</v>
       </c>
       <c r="C108" t="s">
         <v>23</v>
@@ -3375,15 +3372,15 @@
         <v>31</v>
       </c>
       <c r="F108" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B109" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C109" t="s">
         <v>23</v>
@@ -3392,19 +3389,19 @@
         <v>24</v>
       </c>
       <c r="E109" t="s">
+        <v>100</v>
+      </c>
+      <c r="F109" t="s">
         <v>101</v>
-      </c>
-      <c r="F109" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>205</v>
+      </c>
+      <c r="B110" t="s">
         <v>206</v>
       </c>
-      <c r="B110" t="s">
-        <v>207</v>
-      </c>
       <c r="C110" t="s">
         <v>23</v>
       </c>
@@ -3412,19 +3409,19 @@
         <v>24</v>
       </c>
       <c r="E110" t="s">
+        <v>79</v>
+      </c>
+      <c r="F110" t="s">
         <v>80</v>
-      </c>
-      <c r="F110" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>90</v>
+      </c>
+      <c r="B111" t="s">
         <v>91</v>
       </c>
-      <c r="B111" t="s">
-        <v>92</v>
-      </c>
       <c r="C111" t="s">
         <v>23</v>
       </c>
@@ -3432,19 +3429,19 @@
         <v>24</v>
       </c>
       <c r="E111" t="s">
+        <v>196</v>
+      </c>
+      <c r="F111" t="s">
         <v>197</v>
-      </c>
-      <c r="F111" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>74</v>
+      </c>
+      <c r="B112" t="s">
         <v>75</v>
       </c>
-      <c r="B112" t="s">
-        <v>76</v>
-      </c>
       <c r="C112" t="s">
         <v>23</v>
       </c>
@@ -3452,19 +3449,19 @@
         <v>24</v>
       </c>
       <c r="E112" t="s">
+        <v>61</v>
+      </c>
+      <c r="F112" t="s">
         <v>62</v>
-      </c>
-      <c r="F112" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>229</v>
+      </c>
+      <c r="B113" t="s">
         <v>230</v>
       </c>
-      <c r="B113" t="s">
-        <v>231</v>
-      </c>
       <c r="C113" t="s">
         <v>23</v>
       </c>
@@ -3472,18 +3469,18 @@
         <v>24</v>
       </c>
       <c r="E113" t="s">
+        <v>61</v>
+      </c>
+      <c r="F113" t="s">
         <v>62</v>
-      </c>
-      <c r="F113" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B114" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C114" t="s">
         <v>23</v>
@@ -3492,19 +3489,19 @@
         <v>24</v>
       </c>
       <c r="E114" t="s">
+        <v>61</v>
+      </c>
+      <c r="F114" t="s">
         <v>62</v>
-      </c>
-      <c r="F114" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>76</v>
+      </c>
+      <c r="B115" t="s">
         <v>77</v>
       </c>
-      <c r="B115" t="s">
-        <v>78</v>
-      </c>
       <c r="C115" t="s">
         <v>23</v>
       </c>
@@ -3512,18 +3509,18 @@
         <v>24</v>
       </c>
       <c r="E115" t="s">
+        <v>61</v>
+      </c>
+      <c r="F115" t="s">
         <v>62</v>
-      </c>
-      <c r="F115" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B116" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
@@ -3532,18 +3529,18 @@
         <v>24</v>
       </c>
       <c r="E116" t="s">
+        <v>61</v>
+      </c>
+      <c r="F116" t="s">
         <v>62</v>
-      </c>
-      <c r="F116" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B117" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C117" t="s">
         <v>23</v>
@@ -3552,18 +3549,18 @@
         <v>24</v>
       </c>
       <c r="E117" t="s">
+        <v>79</v>
+      </c>
+      <c r="F117" t="s">
         <v>80</v>
-      </c>
-      <c r="F117" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B118" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C118" t="s">
         <v>23</v>
@@ -3572,19 +3569,19 @@
         <v>24</v>
       </c>
       <c r="E118" t="s">
+        <v>79</v>
+      </c>
+      <c r="F118" t="s">
         <v>80</v>
-      </c>
-      <c r="F118" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>65</v>
+      </c>
+      <c r="B119" t="s">
         <v>66</v>
       </c>
-      <c r="B119" t="s">
-        <v>67</v>
-      </c>
       <c r="C119" t="s">
         <v>23</v>
       </c>
@@ -3592,19 +3589,19 @@
         <v>24</v>
       </c>
       <c r="E119" t="s">
+        <v>61</v>
+      </c>
+      <c r="F119" t="s">
         <v>62</v>
-      </c>
-      <c r="F119" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>234</v>
+      </c>
+      <c r="B120" t="s">
         <v>235</v>
       </c>
-      <c r="B120" t="s">
-        <v>236</v>
-      </c>
       <c r="C120" t="s">
         <v>23</v>
       </c>
@@ -3612,18 +3609,18 @@
         <v>24</v>
       </c>
       <c r="E120" t="s">
+        <v>61</v>
+      </c>
+      <c r="F120" t="s">
         <v>62</v>
-      </c>
-      <c r="F120" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B121" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C121" t="s">
         <v>23</v>
@@ -3635,16 +3632,16 @@
         <v>31</v>
       </c>
       <c r="F121" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" t="s">
         <v>243</v>
       </c>
-      <c r="B122" t="s">
-        <v>244</v>
-      </c>
       <c r="C122" t="s">
         <v>23</v>
       </c>
@@ -3652,18 +3649,18 @@
         <v>24</v>
       </c>
       <c r="E122" t="s">
+        <v>249</v>
+      </c>
+      <c r="F122" t="s">
         <v>250</v>
-      </c>
-      <c r="F122" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>244</v>
+      </c>
+      <c r="B123" t="s">
         <v>245</v>
-      </c>
-      <c r="B123" t="s">
-        <v>246</v>
       </c>
       <c r="C123" t="s">
         <v>23</v>
@@ -3675,16 +3672,16 @@
         <v>31</v>
       </c>
       <c r="F123" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" t="s">
         <v>247</v>
       </c>
-      <c r="B124" t="s">
-        <v>248</v>
-      </c>
       <c r="C124" t="s">
         <v>23</v>
       </c>
@@ -3692,18 +3689,18 @@
         <v>24</v>
       </c>
       <c r="E124" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F124" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B125" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C125" t="s">
         <v>23</v>
@@ -3715,15 +3712,15 @@
         <v>31</v>
       </c>
       <c r="F125" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>251</v>
+      </c>
+      <c r="B126" t="s">
         <v>252</v>
-      </c>
-      <c r="B126" t="s">
-        <v>253</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
@@ -3735,7 +3732,7 @@
         <v>31</v>
       </c>
       <c r="F126" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3743,7 +3740,7 @@
         <v>45</v>
       </c>
       <c r="B127" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C127" t="s">
         <v>23</v>
@@ -3755,35 +3752,35 @@
         <v>31</v>
       </c>
       <c r="F127" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>254</v>
+      </c>
+      <c r="B128" t="s">
         <v>255</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
+        <v>23</v>
+      </c>
+      <c r="D128" t="s">
+        <v>24</v>
+      </c>
+      <c r="E128" t="s">
+        <v>249</v>
+      </c>
+      <c r="F128" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>256</v>
       </c>
-      <c r="C128" t="s">
-        <v>23</v>
-      </c>
-      <c r="D128" t="s">
-        <v>24</v>
-      </c>
-      <c r="E128" t="s">
-        <v>250</v>
-      </c>
-      <c r="F128" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="B129" t="s">
         <v>257</v>
-      </c>
-      <c r="B129" t="s">
-        <v>258</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
@@ -3795,15 +3792,15 @@
         <v>31</v>
       </c>
       <c r="F129" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>258</v>
+      </c>
+      <c r="B130" t="s">
         <v>259</v>
-      </c>
-      <c r="B130" t="s">
-        <v>260</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
@@ -3815,15 +3812,15 @@
         <v>31</v>
       </c>
       <c r="F130" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>260</v>
+      </c>
+      <c r="B131" t="s">
         <v>261</v>
-      </c>
-      <c r="B131" t="s">
-        <v>262</v>
       </c>
       <c r="C131" t="s">
         <v>23</v>
@@ -3835,35 +3832,35 @@
         <v>31</v>
       </c>
       <c r="F131" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>262</v>
+      </c>
+      <c r="B132" t="s">
         <v>263</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
+        <v>23</v>
+      </c>
+      <c r="D132" t="s">
+        <v>24</v>
+      </c>
+      <c r="E132" t="s">
+        <v>163</v>
+      </c>
+      <c r="F132" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>264</v>
       </c>
-      <c r="C132" t="s">
-        <v>23</v>
-      </c>
-      <c r="D132" t="s">
-        <v>24</v>
-      </c>
-      <c r="E132" t="s">
-        <v>164</v>
-      </c>
-      <c r="F132" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="B133" t="s">
         <v>265</v>
-      </c>
-      <c r="B133" t="s">
-        <v>266</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -3875,36 +3872,36 @@
         <v>31</v>
       </c>
       <c r="F133" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B134" t="s">
+        <v>266</v>
+      </c>
+      <c r="C134" t="s">
+        <v>23</v>
+      </c>
+      <c r="D134" t="s">
+        <v>24</v>
+      </c>
+      <c r="E134" t="s">
+        <v>61</v>
+      </c>
+      <c r="F134" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>267</v>
       </c>
-      <c r="C134" t="s">
-        <v>23</v>
-      </c>
-      <c r="D134" t="s">
-        <v>24</v>
-      </c>
-      <c r="E134" t="s">
-        <v>62</v>
-      </c>
-      <c r="F134" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="B135" t="s">
         <v>268</v>
       </c>
-      <c r="B135" t="s">
-        <v>269</v>
-      </c>
       <c r="C135" t="s">
         <v>23</v>
       </c>
@@ -3912,21 +3909,11 @@
         <v>24</v>
       </c>
       <c r="E135" t="s">
+        <v>79</v>
+      </c>
+      <c r="F135" t="s">
         <v>80</v>
       </c>
-      <c r="F135" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="1"/>
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
-      <c r="E140" s="1"/>
-      <c r="F140" s="1"/>
-      <c r="G140" s="1"/>
-      <c r="H140" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/shops.xlsx
+++ b/shops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/512a546b848d6679/سطح المكتب/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="431" documentId="11_9888CF1E5976440F62355476585DCE3A474BFA2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{012873F6-791F-446A-AED9-2F3C028F514F}"/>
+  <xr:revisionPtr revIDLastSave="612" documentId="11_9888CF1E5976440F62355476585DCE3A474BFA2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AED2C7DB-479D-466F-9703-E49721E03C14}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="316">
   <si>
     <t>اسم المحل</t>
   </si>
@@ -400,9 +400,6 @@
     <t>Nursery</t>
   </si>
   <si>
-    <t>حضانة</t>
-  </si>
-  <si>
     <t>Shoe Express</t>
   </si>
   <si>
@@ -628,9 +625,6 @@
     <t>Match</t>
   </si>
   <si>
-    <t>بلو ايدج</t>
-  </si>
-  <si>
     <t>بالمان</t>
   </si>
   <si>
@@ -643,12 +637,6 @@
     <t>Paul</t>
   </si>
   <si>
-    <t>بيتزا لاين</t>
-  </si>
-  <si>
-    <t>Pizza Line</t>
-  </si>
-  <si>
     <t>سبأ</t>
   </si>
   <si>
@@ -676,9 +664,6 @@
     <t>Domino's</t>
   </si>
   <si>
-    <t>لافيان كافيه</t>
-  </si>
-  <si>
     <t>Lavian Cafe</t>
   </si>
   <si>
@@ -754,12 +739,6 @@
     <t>Salam</t>
   </si>
   <si>
-    <t>أطياب المرشود</t>
-  </si>
-  <si>
-    <t>Atyab Al Marshoud</t>
-  </si>
-  <si>
     <t>لولو جلاس</t>
   </si>
   <si>
@@ -836,13 +815,166 @@
   </si>
   <si>
     <t xml:space="preserve">كمبير </t>
+  </si>
+  <si>
+    <t>اساور رنيم</t>
+  </si>
+  <si>
+    <t>Ranim's bracelets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لذة حلا </t>
+  </si>
+  <si>
+    <t>أصول الحلا</t>
+  </si>
+  <si>
+    <t>Ouswl of hala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue star </t>
+  </si>
+  <si>
+    <t>لافينا كافيه</t>
+  </si>
+  <si>
+    <t>بلو ايج</t>
+  </si>
+  <si>
+    <t>حضانة سارة</t>
+  </si>
+  <si>
+    <t>أطفال علماء</t>
+  </si>
+  <si>
+    <t>kids Scientists</t>
+  </si>
+  <si>
+    <t>الحميضي</t>
+  </si>
+  <si>
+    <t>يولا</t>
+  </si>
+  <si>
+    <t>Yola</t>
+  </si>
+  <si>
+    <t>Mumuso</t>
+  </si>
+  <si>
+    <t>Kids barber</t>
+  </si>
+  <si>
+    <t>كيدز باربر</t>
+  </si>
+  <si>
+    <t>لميس</t>
+  </si>
+  <si>
+    <t>Lamais</t>
+  </si>
+  <si>
+    <t>Al jarboua</t>
+  </si>
+  <si>
+    <t>الجربوع</t>
+  </si>
+  <si>
+    <t>اوبشن بي</t>
+  </si>
+  <si>
+    <t>Option B</t>
+  </si>
+  <si>
+    <t>Fitness fruit</t>
+  </si>
+  <si>
+    <t>فتنس فروت</t>
+  </si>
+  <si>
+    <t>بولو</t>
+  </si>
+  <si>
+    <t>Polo</t>
+  </si>
+  <si>
+    <t>Mansor rashwan</t>
+  </si>
+  <si>
+    <t>منصور رشوان</t>
+  </si>
+  <si>
+    <t>كراميل باث اند بدي</t>
+  </si>
+  <si>
+    <t>Caramel bath &amp; body</t>
+  </si>
+  <si>
+    <t>Movenpick</t>
+  </si>
+  <si>
+    <t>موفنبيك</t>
+  </si>
+  <si>
+    <t>دلع</t>
+  </si>
+  <si>
+    <t>Dala</t>
+  </si>
+  <si>
+    <t>قصة</t>
+  </si>
+  <si>
+    <t>Gissah</t>
+  </si>
+  <si>
+    <t>Osma</t>
+  </si>
+  <si>
+    <t>اوسما</t>
+  </si>
+  <si>
+    <t>موج فون</t>
+  </si>
+  <si>
+    <t>Mooj phone</t>
+  </si>
+  <si>
+    <t>ستي روز</t>
+  </si>
+  <si>
+    <t>City rose</t>
+  </si>
+  <si>
+    <t>Ghanati</t>
+  </si>
+  <si>
+    <t>غناتي</t>
+  </si>
+  <si>
+    <t>LE Vian</t>
+  </si>
+  <si>
+    <t>مكينة حلوى غزل البنات</t>
+  </si>
+  <si>
+    <t>Cotton Candy Machine</t>
+  </si>
+  <si>
+    <t>العاب سيارات متجولة</t>
+  </si>
+  <si>
+    <t>Baby cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alhomaidhi </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -854,6 +986,12 @@
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -891,11 +1029,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -1202,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -1657,7 +1796,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s">
         <v>125</v>
@@ -1680,7 +1819,7 @@
         <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
@@ -1697,10 +1836,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" t="s">
         <v>128</v>
-      </c>
-      <c r="B25" t="s">
-        <v>129</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
@@ -1712,12 +1851,12 @@
         <v>79</v>
       </c>
       <c r="F25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B26" t="s">
         <v>39</v>
@@ -1732,15 +1871,15 @@
         <v>31</v>
       </c>
       <c r="F26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" t="s">
         <v>133</v>
-      </c>
-      <c r="B27" t="s">
-        <v>134</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
@@ -1777,10 +1916,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
@@ -1792,35 +1931,35 @@
         <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" t="s">
         <v>138</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" t="s">
         <v>139</v>
       </c>
-      <c r="C30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>140</v>
-      </c>
-      <c r="F30" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
@@ -1832,15 +1971,15 @@
         <v>29</v>
       </c>
       <c r="F31" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>143</v>
+      </c>
+      <c r="B32" t="s">
         <v>144</v>
-      </c>
-      <c r="B32" t="s">
-        <v>145</v>
       </c>
       <c r="C32" t="s">
         <v>23</v>
@@ -1852,15 +1991,15 @@
         <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C33" t="s">
         <v>23</v>
@@ -1869,7 +2008,7 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F33" t="s">
         <v>48</v>
@@ -1877,10 +2016,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
@@ -1900,7 +2039,7 @@
         <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
@@ -1909,7 +2048,7 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F35" t="s">
         <v>48</v>
@@ -1937,10 +2076,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
@@ -1957,10 +2096,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
@@ -1972,12 +2111,12 @@
         <v>31</v>
       </c>
       <c r="F38" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
@@ -1997,10 +2136,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B40" t="s">
         <v>179</v>
-      </c>
-      <c r="B40" t="s">
-        <v>180</v>
       </c>
       <c r="C40" t="s">
         <v>23</v>
@@ -2017,11 +2156,11 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>180</v>
+      </c>
+      <c r="B41" t="s">
         <v>181</v>
       </c>
-      <c r="B41" t="s">
-        <v>182</v>
-      </c>
       <c r="C41" t="s">
         <v>23</v>
       </c>
@@ -2029,7 +2168,7 @@
         <v>24</v>
       </c>
       <c r="E41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F41" t="s">
         <v>48</v>
@@ -2060,7 +2199,7 @@
         <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
@@ -2089,7 +2228,7 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F44" t="s">
         <v>48</v>
@@ -2097,10 +2236,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C45" t="s">
         <v>23</v>
@@ -2109,7 +2248,7 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F45" t="s">
         <v>48</v>
@@ -2132,15 +2271,15 @@
         <v>31</v>
       </c>
       <c r="F46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B47" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
@@ -2149,7 +2288,7 @@
         <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F47" t="s">
         <v>48</v>
@@ -2157,7 +2296,7 @@
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
@@ -2177,7 +2316,7 @@
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
@@ -2212,15 +2351,15 @@
         <v>29</v>
       </c>
       <c r="F50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B51" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C51" t="s">
         <v>23</v>
@@ -2232,12 +2371,12 @@
         <v>31</v>
       </c>
       <c r="F51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B52" t="s">
         <v>40</v>
@@ -2252,15 +2391,15 @@
         <v>31</v>
       </c>
       <c r="F52" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
@@ -2277,10 +2416,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C54" t="s">
         <v>23</v>
@@ -2289,10 +2428,10 @@
         <v>24</v>
       </c>
       <c r="E54" t="s">
+        <v>139</v>
+      </c>
+      <c r="F54" t="s">
         <v>140</v>
-      </c>
-      <c r="F54" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2300,7 +2439,7 @@
         <v>41</v>
       </c>
       <c r="B55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C55" t="s">
         <v>23</v>
@@ -2312,12 +2451,12 @@
         <v>31</v>
       </c>
       <c r="F55" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B56" t="s">
         <v>20</v>
@@ -2337,10 +2476,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C57" t="s">
         <v>23</v>
@@ -2352,15 +2491,15 @@
         <v>31</v>
       </c>
       <c r="F57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>184</v>
+      </c>
+      <c r="B58" t="s">
         <v>185</v>
-      </c>
-      <c r="B58" t="s">
-        <v>186</v>
       </c>
       <c r="C58" t="s">
         <v>23</v>
@@ -2377,10 +2516,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B59" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" t="s">
         <v>7</v>
@@ -2412,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="F60" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2420,7 +2559,7 @@
         <v>50</v>
       </c>
       <c r="B61" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -2429,7 +2568,7 @@
         <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F61" t="s">
         <v>48</v>
@@ -2440,7 +2579,7 @@
         <v>53</v>
       </c>
       <c r="B62" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C62" t="s">
         <v>23</v>
@@ -2449,7 +2588,7 @@
         <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F62" t="s">
         <v>48</v>
@@ -2457,10 +2596,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B63" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C63" t="s">
         <v>23</v>
@@ -2489,7 +2628,7 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F64" t="s">
         <v>48</v>
@@ -2497,10 +2636,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B65" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
@@ -2517,10 +2656,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B66" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" t="s">
         <v>23</v>
@@ -2537,10 +2676,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B67" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C67" t="s">
         <v>7</v>
@@ -2557,7 +2696,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
@@ -2577,7 +2716,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
@@ -2597,7 +2736,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
@@ -2617,7 +2756,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
@@ -2637,7 +2776,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
@@ -2657,7 +2796,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
@@ -2677,10 +2816,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B74" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C74" t="s">
         <v>23</v>
@@ -2692,15 +2831,15 @@
         <v>31</v>
       </c>
       <c r="F74" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>190</v>
+      </c>
+      <c r="B75" t="s">
         <v>191</v>
-      </c>
-      <c r="B75" t="s">
-        <v>192</v>
       </c>
       <c r="C75" t="s">
         <v>23</v>
@@ -2712,12 +2851,12 @@
         <v>31</v>
       </c>
       <c r="F75" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>
@@ -2737,7 +2876,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B77" t="s">
         <v>6</v>
@@ -2757,7 +2896,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B78" t="s">
         <v>6</v>
@@ -2780,7 +2919,7 @@
         <v>35</v>
       </c>
       <c r="B79" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C79" t="s">
         <v>23</v>
@@ -2792,7 +2931,7 @@
         <v>31</v>
       </c>
       <c r="F79" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2820,7 +2959,7 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C81" t="s">
         <v>23</v>
@@ -2829,10 +2968,10 @@
         <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F81" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2840,7 +2979,7 @@
         <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
@@ -2852,7 +2991,7 @@
         <v>31</v>
       </c>
       <c r="F82" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2860,7 +2999,7 @@
         <v>30</v>
       </c>
       <c r="B83" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
@@ -2872,15 +3011,15 @@
         <v>31</v>
       </c>
       <c r="F83" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B84" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C84" t="s">
         <v>23</v>
@@ -2892,15 +3031,15 @@
         <v>31</v>
       </c>
       <c r="F84" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>199</v>
+      </c>
+      <c r="B85" t="s">
         <v>200</v>
-      </c>
-      <c r="B85" t="s">
-        <v>201</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
@@ -2912,7 +3051,7 @@
         <v>31</v>
       </c>
       <c r="F85" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2932,12 +3071,12 @@
         <v>31</v>
       </c>
       <c r="F86" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="B87" t="s">
         <v>10</v>
@@ -2957,7 +3096,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="B88" t="s">
         <v>10</v>
@@ -2997,10 +3136,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B90" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C90" t="s">
         <v>17</v>
@@ -3017,10 +3156,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B91" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C91" t="s">
         <v>23</v>
@@ -3057,10 +3196,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>207</v>
+        <v>63</v>
       </c>
       <c r="B93" t="s">
-        <v>208</v>
+        <v>64</v>
       </c>
       <c r="C93" t="s">
         <v>23</v>
@@ -3077,10 +3216,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="B94" t="s">
-        <v>64</v>
+        <v>206</v>
       </c>
       <c r="C94" t="s">
         <v>23</v>
@@ -3097,10 +3236,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B95" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C95" t="s">
         <v>23</v>
@@ -3117,10 +3256,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>211</v>
+        <v>70</v>
       </c>
       <c r="B96" t="s">
-        <v>212</v>
+        <v>71</v>
       </c>
       <c r="C96" t="s">
         <v>23</v>
@@ -3137,10 +3276,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B97" t="s">
-        <v>71</v>
+        <v>236</v>
       </c>
       <c r="C97" t="s">
         <v>23</v>
@@ -3157,10 +3296,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>72</v>
+        <v>209</v>
       </c>
       <c r="B98" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="C98" t="s">
         <v>23</v>
@@ -3177,10 +3316,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B99" t="s">
-        <v>214</v>
+        <v>73</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
@@ -3197,10 +3336,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B100" t="s">
-        <v>73</v>
+        <v>213</v>
       </c>
       <c r="C100" t="s">
         <v>23</v>
@@ -3217,10 +3356,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>216</v>
+        <v>271</v>
       </c>
       <c r="B101" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C101" t="s">
         <v>23</v>
@@ -3229,18 +3368,18 @@
         <v>24</v>
       </c>
       <c r="E101" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="F101" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B102" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C102" t="s">
         <v>23</v>
@@ -3249,18 +3388,18 @@
         <v>24</v>
       </c>
       <c r="E102" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="F102" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B103" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
@@ -3272,15 +3411,15 @@
         <v>31</v>
       </c>
       <c r="F103" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>222</v>
+        <v>58</v>
       </c>
       <c r="B104" t="s">
-        <v>222</v>
+        <v>59</v>
       </c>
       <c r="C104" t="s">
         <v>23</v>
@@ -3289,18 +3428,18 @@
         <v>24</v>
       </c>
       <c r="E104" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F104" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="B105" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
@@ -3309,58 +3448,58 @@
         <v>24</v>
       </c>
       <c r="E105" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F105" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="C106" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D106" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E106" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F106" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B107" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C107" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D107" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E107" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F107" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B108" t="s">
-        <v>227</v>
+        <v>102</v>
       </c>
       <c r="C108" t="s">
         <v>23</v>
@@ -3369,18 +3508,18 @@
         <v>24</v>
       </c>
       <c r="E108" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="F108" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="B109" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="C109" t="s">
         <v>23</v>
@@ -3389,18 +3528,18 @@
         <v>24</v>
       </c>
       <c r="E109" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="F109" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>205</v>
+        <v>90</v>
       </c>
       <c r="B110" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="C110" t="s">
         <v>23</v>
@@ -3409,18 +3548,18 @@
         <v>24</v>
       </c>
       <c r="E110" t="s">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="F110" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B111" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C111" t="s">
         <v>23</v>
@@ -3429,18 +3568,18 @@
         <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>196</v>
+        <v>61</v>
       </c>
       <c r="F111" t="s">
-        <v>197</v>
+        <v>62</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="B112" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="C112" t="s">
         <v>23</v>
@@ -3457,10 +3596,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B113" t="s">
-        <v>230</v>
+        <v>67</v>
       </c>
       <c r="C113" t="s">
         <v>23</v>
@@ -3477,10 +3616,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>231</v>
+        <v>76</v>
       </c>
       <c r="B114" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C114" t="s">
         <v>23</v>
@@ -3497,10 +3636,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>76</v>
+        <v>227</v>
       </c>
       <c r="B115" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C115" t="s">
         <v>23</v>
@@ -3517,10 +3656,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>232</v>
+        <v>85</v>
       </c>
       <c r="B116" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
@@ -3529,18 +3668,18 @@
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="F116" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="B117" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C117" t="s">
         <v>23</v>
@@ -3557,10 +3696,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="B118" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C118" t="s">
         <v>23</v>
@@ -3569,18 +3708,18 @@
         <v>24</v>
       </c>
       <c r="E118" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F118" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>65</v>
+        <v>229</v>
       </c>
       <c r="B119" t="s">
-        <v>66</v>
+        <v>230</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -3597,10 +3736,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="B120" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="C120" t="s">
         <v>23</v>
@@ -3609,18 +3748,18 @@
         <v>24</v>
       </c>
       <c r="E120" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="F120" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="B121" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="C121" t="s">
         <v>23</v>
@@ -3629,18 +3768,18 @@
         <v>24</v>
       </c>
       <c r="E121" t="s">
-        <v>31</v>
+        <v>242</v>
       </c>
       <c r="F121" t="s">
-        <v>132</v>
+        <v>243</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B122" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C122" t="s">
         <v>23</v>
@@ -3649,18 +3788,18 @@
         <v>24</v>
       </c>
       <c r="E122" t="s">
-        <v>249</v>
+        <v>162</v>
       </c>
       <c r="F122" t="s">
-        <v>250</v>
+        <v>48</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="B123" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C123" t="s">
         <v>23</v>
@@ -3672,15 +3811,15 @@
         <v>31</v>
       </c>
       <c r="F123" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B124" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C124" t="s">
         <v>23</v>
@@ -3689,18 +3828,18 @@
         <v>24</v>
       </c>
       <c r="E124" t="s">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c r="F124" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="B125" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C125" t="s">
         <v>23</v>
@@ -3712,15 +3851,15 @@
         <v>31</v>
       </c>
       <c r="F125" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B126" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
@@ -3729,18 +3868,18 @@
         <v>24</v>
       </c>
       <c r="E126" t="s">
-        <v>31</v>
+        <v>242</v>
       </c>
       <c r="F126" t="s">
-        <v>132</v>
+        <v>243</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>45</v>
+        <v>249</v>
       </c>
       <c r="B127" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C127" t="s">
         <v>23</v>
@@ -3752,15 +3891,15 @@
         <v>31</v>
       </c>
       <c r="F127" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B128" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
@@ -3769,18 +3908,18 @@
         <v>24</v>
       </c>
       <c r="E128" t="s">
-        <v>249</v>
+        <v>31</v>
       </c>
       <c r="F128" t="s">
-        <v>250</v>
+        <v>131</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B129" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
@@ -3792,15 +3931,15 @@
         <v>31</v>
       </c>
       <c r="F129" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B130" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
@@ -3809,18 +3948,18 @@
         <v>24</v>
       </c>
       <c r="E130" t="s">
-        <v>31</v>
+        <v>162</v>
       </c>
       <c r="F130" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B131" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C131" t="s">
         <v>23</v>
@@ -3832,15 +3971,15 @@
         <v>31</v>
       </c>
       <c r="F131" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B132" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C132" t="s">
         <v>23</v>
@@ -3849,18 +3988,18 @@
         <v>24</v>
       </c>
       <c r="E132" t="s">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="F132" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B133" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -3869,15 +4008,15 @@
         <v>24</v>
       </c>
       <c r="E133" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="F133" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B134" t="s">
         <v>266</v>
@@ -3889,10 +4028,10 @@
         <v>24</v>
       </c>
       <c r="E134" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="F134" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3900,22 +4039,643 @@
         <v>267</v>
       </c>
       <c r="B135" t="s">
+        <v>267</v>
+      </c>
+      <c r="C135" t="s">
+        <v>23</v>
+      </c>
+      <c r="D135" t="s">
+        <v>24</v>
+      </c>
+      <c r="E135" t="s">
+        <v>195</v>
+      </c>
+      <c r="F135" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>268</v>
       </c>
-      <c r="C135" t="s">
-        <v>23</v>
-      </c>
-      <c r="D135" t="s">
-        <v>24</v>
-      </c>
-      <c r="E135" t="s">
+      <c r="B136" t="s">
+        <v>269</v>
+      </c>
+      <c r="C136" t="s">
+        <v>23</v>
+      </c>
+      <c r="D136" t="s">
+        <v>24</v>
+      </c>
+      <c r="E136" t="s">
+        <v>195</v>
+      </c>
+      <c r="F136" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>127</v>
+      </c>
+      <c r="B137" t="s">
+        <v>270</v>
+      </c>
+      <c r="C137" t="s">
+        <v>23</v>
+      </c>
+      <c r="D137" t="s">
+        <v>24</v>
+      </c>
+      <c r="E137" t="s">
         <v>79</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F137" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>127</v>
+      </c>
+      <c r="B138" t="s">
+        <v>270</v>
+      </c>
+      <c r="C138" t="s">
+        <v>23</v>
+      </c>
+      <c r="D138" t="s">
+        <v>24</v>
+      </c>
+      <c r="E138" t="s">
+        <v>232</v>
+      </c>
+      <c r="F138" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>201</v>
+      </c>
+      <c r="B139" t="s">
+        <v>202</v>
+      </c>
+      <c r="C139" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" t="s">
+        <v>9</v>
+      </c>
+      <c r="F139" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>13</v>
+      </c>
+      <c r="B140" t="s">
+        <v>106</v>
+      </c>
+      <c r="C140" t="s">
+        <v>23</v>
+      </c>
+      <c r="D140" t="s">
+        <v>24</v>
+      </c>
+      <c r="E140" t="s">
+        <v>93</v>
+      </c>
+      <c r="F140" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>14</v>
+      </c>
+      <c r="B141" t="s">
+        <v>15</v>
+      </c>
+      <c r="C141" t="s">
+        <v>23</v>
+      </c>
+      <c r="D141" t="s">
+        <v>24</v>
+      </c>
+      <c r="E141" t="s">
+        <v>93</v>
+      </c>
+      <c r="F141" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>274</v>
+      </c>
+      <c r="B142" t="s">
+        <v>275</v>
+      </c>
+      <c r="C142" t="s">
+        <v>21</v>
+      </c>
+      <c r="D142" t="s">
+        <v>22</v>
+      </c>
+      <c r="E142" t="s">
+        <v>120</v>
+      </c>
+      <c r="F142" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>276</v>
+      </c>
+      <c r="B143" t="s">
+        <v>315</v>
+      </c>
+      <c r="C143" t="s">
+        <v>23</v>
+      </c>
+      <c r="D143" t="s">
+        <v>24</v>
+      </c>
+      <c r="E143" t="s">
+        <v>162</v>
+      </c>
+      <c r="F143" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>277</v>
+      </c>
+      <c r="B144" t="s">
+        <v>278</v>
+      </c>
+      <c r="C144" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" t="s">
+        <v>9</v>
+      </c>
+      <c r="F144" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>279</v>
+      </c>
+      <c r="B145" t="s">
+        <v>279</v>
+      </c>
+      <c r="C145" t="s">
+        <v>23</v>
+      </c>
+      <c r="D145" t="s">
+        <v>24</v>
+      </c>
+      <c r="E145" t="s">
+        <v>93</v>
+      </c>
+      <c r="F145" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>281</v>
+      </c>
+      <c r="B146" t="s">
+        <v>280</v>
+      </c>
+      <c r="C146" t="s">
+        <v>21</v>
+      </c>
+      <c r="D146" t="s">
+        <v>22</v>
+      </c>
+      <c r="E146" t="s">
+        <v>120</v>
+      </c>
+      <c r="F146" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>282</v>
+      </c>
+      <c r="B147" t="s">
+        <v>283</v>
+      </c>
+      <c r="C147" t="s">
+        <v>23</v>
+      </c>
+      <c r="D147" t="s">
+        <v>24</v>
+      </c>
+      <c r="E147" t="s">
+        <v>56</v>
+      </c>
+      <c r="F147" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>285</v>
+      </c>
+      <c r="B148" t="s">
+        <v>284</v>
+      </c>
+      <c r="C148" t="s">
+        <v>23</v>
+      </c>
+      <c r="D148" t="s">
+        <v>24</v>
+      </c>
+      <c r="E148" t="s">
+        <v>162</v>
+      </c>
+      <c r="F148" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>286</v>
+      </c>
+      <c r="B149" t="s">
+        <v>287</v>
+      </c>
+      <c r="C149" t="s">
+        <v>23</v>
+      </c>
+      <c r="D149" t="s">
+        <v>24</v>
+      </c>
+      <c r="E149" t="s">
+        <v>31</v>
+      </c>
+      <c r="F149" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>289</v>
+      </c>
+      <c r="B150" t="s">
+        <v>288</v>
+      </c>
+      <c r="C150" t="s">
+        <v>23</v>
+      </c>
+      <c r="D150" t="s">
+        <v>24</v>
+      </c>
+      <c r="E150" t="s">
+        <v>61</v>
+      </c>
+      <c r="F150" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>290</v>
+      </c>
+      <c r="B151" t="s">
+        <v>291</v>
+      </c>
+      <c r="C151" t="s">
+        <v>7</v>
+      </c>
+      <c r="D151" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151" t="s">
+        <v>9</v>
+      </c>
+      <c r="F151" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>290</v>
+      </c>
+      <c r="B152" t="s">
+        <v>291</v>
+      </c>
+      <c r="C152" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152" t="s">
+        <v>9</v>
+      </c>
+      <c r="F152" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>290</v>
+      </c>
+      <c r="B153" t="s">
+        <v>291</v>
+      </c>
+      <c r="C153" t="s">
+        <v>23</v>
+      </c>
+      <c r="D153" t="s">
+        <v>24</v>
+      </c>
+      <c r="E153" t="s">
+        <v>56</v>
+      </c>
+      <c r="F153" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>293</v>
+      </c>
+      <c r="B154" t="s">
+        <v>292</v>
+      </c>
+      <c r="C154" t="s">
+        <v>23</v>
+      </c>
+      <c r="D154" t="s">
+        <v>24</v>
+      </c>
+      <c r="E154" t="s">
+        <v>162</v>
+      </c>
+      <c r="F154" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>294</v>
+      </c>
+      <c r="B155" t="s">
+        <v>295</v>
+      </c>
+      <c r="C155" t="s">
+        <v>23</v>
+      </c>
+      <c r="D155" t="s">
+        <v>24</v>
+      </c>
+      <c r="E155" t="s">
+        <v>31</v>
+      </c>
+      <c r="F155" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>297</v>
+      </c>
+      <c r="B156" t="s">
+        <v>296</v>
+      </c>
+      <c r="C156" t="s">
+        <v>23</v>
+      </c>
+      <c r="D156" t="s">
+        <v>24</v>
+      </c>
+      <c r="E156" t="s">
+        <v>195</v>
+      </c>
+      <c r="F156" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>298</v>
+      </c>
+      <c r="B157" t="s">
+        <v>299</v>
+      </c>
+      <c r="C157" t="s">
+        <v>23</v>
+      </c>
+      <c r="D157" t="s">
+        <v>24</v>
+      </c>
+      <c r="E157" t="s">
+        <v>162</v>
+      </c>
+      <c r="F157" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>300</v>
+      </c>
+      <c r="B158" t="s">
+        <v>301</v>
+      </c>
+      <c r="C158" t="s">
+        <v>23</v>
+      </c>
+      <c r="D158" t="s">
+        <v>24</v>
+      </c>
+      <c r="E158" t="s">
+        <v>31</v>
+      </c>
+      <c r="F158" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>303</v>
+      </c>
+      <c r="B159" t="s">
+        <v>302</v>
+      </c>
+      <c r="C159" t="s">
+        <v>23</v>
+      </c>
+      <c r="D159" t="s">
+        <v>24</v>
+      </c>
+      <c r="E159" t="s">
+        <v>31</v>
+      </c>
+      <c r="F159" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>304</v>
+      </c>
+      <c r="B160" t="s">
+        <v>305</v>
+      </c>
+      <c r="C160" t="s">
+        <v>23</v>
+      </c>
+      <c r="D160" t="s">
+        <v>24</v>
+      </c>
+      <c r="E160" t="s">
+        <v>242</v>
+      </c>
+      <c r="F160" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>306</v>
+      </c>
+      <c r="B161" t="s">
+        <v>307</v>
+      </c>
+      <c r="C161" t="s">
+        <v>23</v>
+      </c>
+      <c r="D161" t="s">
+        <v>24</v>
+      </c>
+      <c r="E161" t="s">
+        <v>242</v>
+      </c>
+      <c r="F161" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>309</v>
+      </c>
+      <c r="B162" t="s">
+        <v>308</v>
+      </c>
+      <c r="C162" t="s">
+        <v>23</v>
+      </c>
+      <c r="D162" t="s">
+        <v>24</v>
+      </c>
+      <c r="E162" t="s">
+        <v>31</v>
+      </c>
+      <c r="F162" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>135</v>
+      </c>
+      <c r="B163" t="s">
+        <v>134</v>
+      </c>
+      <c r="C163" t="s">
+        <v>23</v>
+      </c>
+      <c r="D163" t="s">
+        <v>24</v>
+      </c>
+      <c r="E163" t="s">
+        <v>31</v>
+      </c>
+      <c r="F163" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>310</v>
+      </c>
+      <c r="B164" t="s">
+        <v>310</v>
+      </c>
+      <c r="C164" t="s">
+        <v>23</v>
+      </c>
+      <c r="D164" t="s">
+        <v>24</v>
+      </c>
+      <c r="E164" t="s">
+        <v>162</v>
+      </c>
+      <c r="F164" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>311</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C165" t="s">
+        <v>23</v>
+      </c>
+      <c r="D165" t="s">
+        <v>24</v>
+      </c>
+      <c r="E165" t="s">
+        <v>195</v>
+      </c>
+      <c r="F165" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>313</v>
+      </c>
+      <c r="B166" t="s">
+        <v>314</v>
+      </c>
+      <c r="C166" t="s">
+        <v>21</v>
+      </c>
+      <c r="D166" t="s">
+        <v>22</v>
+      </c>
+      <c r="E166" t="s">
+        <v>120</v>
+      </c>
+      <c r="F166" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>